--- a/output/laminas_comunales/comunal_i_peringrmin_a_2022_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2022_tarapaca.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>8.890000000000001</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>8.07</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>5.97</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>5.61</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>5.44</v>
       </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>5.18</v>
       </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -473,9 +450,6 @@
       </c>
       <c r="B8">
         <v>5.04</v>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_peringrmin_a_2022_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2022_tarapaca.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,6 +391,15 @@
       <c r="B2">
         <v>8.890000000000001</v>
       </c>
+      <c r="C2">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="D2">
+        <v>-0.08000000000000007</v>
+      </c>
+      <c r="E2">
+        <v>-0.8918617614269819</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -411,6 +420,15 @@
       <c r="B4">
         <v>5.97</v>
       </c>
+      <c r="C4">
+        <v>6.12</v>
+      </c>
+      <c r="D4">
+        <v>-0.1500000000000004</v>
+      </c>
+      <c r="E4">
+        <v>-2.450980392156865</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -421,34 +439,80 @@
       <c r="B5">
         <v>5.61</v>
       </c>
+      <c r="C5">
+        <v>5.74</v>
+      </c>
+      <c r="D5">
+        <v>-0.1299999999999999</v>
+      </c>
+      <c r="E5">
+        <v>-2.264808362369342</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Iquique</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B6">
-        <v>5.44</v>
+        <v>5.51</v>
+      </c>
+      <c r="C6">
+        <v>5.72</v>
+      </c>
+      <c r="D6">
+        <v>-0.21</v>
+      </c>
+      <c r="E6">
+        <v>-3.671328671328666</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pozo Almonte</t>
+          <t>Iquique</t>
         </is>
       </c>
       <c r="B7">
-        <v>5.18</v>
+        <v>5.44</v>
+      </c>
+      <c r="C7">
+        <v>5.68</v>
+      </c>
+      <c r="D7">
+        <v>-0.2399999999999993</v>
+      </c>
+      <c r="E7">
+        <v>-4.22535211267604</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>5.18</v>
+      </c>
+      <c r="C8">
+        <v>5.51</v>
+      </c>
+      <c r="D8">
+        <v>-0.3300000000000001</v>
+      </c>
+      <c r="E8">
+        <v>-5.989110707803991</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Colchane</t>
         </is>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>5.04</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_peringrmin_a_2022_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2022_tarapaca.xlsx
@@ -523,7 +523,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -532,40 +532,26 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alto Hospicio</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>5.61</v>
+          <t>Camiña</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Camiña</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>8.07</v>
+          <t>Colchane</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Colchane</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>5.04</v>
+          <t>Pozo Almonte</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -574,38 +560,26 @@
           <t>Huara</t>
         </is>
       </c>
-      <c r="B5">
-        <v>8.890000000000001</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Iquique</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>5.44</v>
+          <t>Alto Hospicio</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pica</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>5.97</v>
+          <t>Iquique</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pozo Almonte</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>5.18</v>
+          <t>Pica</t>
+        </is>
       </c>
     </row>
   </sheetData>
